--- a/02_DIA_inicio_2026_analisis_assets/rbd_9599_liceo-purkuyen_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9599_liceo-purkuyen_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82AE5B0D-1EA1-4DA9-9C44-EAC471380A36}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4401302-3DC4-4A4F-84E7-EA22C52FF4E7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00464204-3D3B-4715-A3ED-F8F3736F75D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76A74384-C448-4F00-93BD-1519415354DA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E34E3124-CA03-4F41-B553-ED03A241C1E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9DF18DA-9364-47C6-B292-3452442398B7}"/>
 </file>